--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-faerbung-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-faerbung-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-faerbung-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-faerbung-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
